--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,103 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129667002</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97598</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vägen mot Simontorp, Vägen mot Simontorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>467807</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6255049</v>
+      </c>
+      <c r="S4" t="n">
+        <v>40</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129659071</v>
       </c>
       <c r="B3" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129659071</v>
       </c>
       <c r="B3" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129659071</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>96026</v>
+        <v>96030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129659071</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129659071</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34204-2025 artfynd.xlsx
+++ b/artfynd/A 34204-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129659099</v>
       </c>
       <c r="B2" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129667002</v>
       </c>
       <c r="B4" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
